--- a/data/fullyear-resilience/Power_VRES.xlsx
+++ b/data/fullyear-resilience/Power_VRES.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\mini-example-resilience\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\fullyear-resilience\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CC92DA0-85DE-46EB-AB55-6E203CD7FDE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF8E5A6-7D41-4964-8C7A-665EB392C4C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioA" sheetId="1" r:id="rId1"/>
+    <sheet name="year2017" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -126,8 +127,102 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{29C73D7A-B357-4CC5-894E-31832403F611}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>If a line has a value in this column, it is not read in (i.e., does not exist).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{1BBB52FB-D310-44EB-B41C-897F69A34CE3}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Readable name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{706D8B0E-3FAB-4A43-890F-B699740F1411}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Value specifier in database</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{508EE005-D3FE-4C78-AE57-6CECDD2B4BD0}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Description</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{4D62E018-7098-4DDA-8690-04FE71D96C8B}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Details on database behavior</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{4888D04D-C556-4E3A-8876-EF3BEB180A18}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Unit or valid values</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="76">
   <si>
     <t>Power - Variable Renewable Energy Sources</t>
   </si>
@@ -1321,4 +1416,525 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0210D501-3301-404E-B3E8-49D24C004ABE}">
+  <sheetPr>
+    <tabColor rgb="FF008080"/>
+  </sheetPr>
+  <dimension ref="A1:U12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="3" max="15" width="15.7109375" customWidth="1"/>
+    <col min="16" max="17" width="20.140625" customWidth="1"/>
+    <col min="18" max="19" width="15.7109375" customWidth="1"/>
+    <col min="20" max="21" width="24.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="S3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="T3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="U3" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="R4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="S4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="T4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="U4" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="R5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="S5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="T5" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="U5" s="7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q6" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="R6" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="S6" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="T6" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="U6" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="P7" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q7" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="R7" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="S7" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="T7" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="U7" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" s="10"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="13">
+        <v>0</v>
+      </c>
+      <c r="G8" s="14">
+        <v>1</v>
+      </c>
+      <c r="H8" s="13">
+        <v>1</v>
+      </c>
+      <c r="I8" s="13">
+        <v>20</v>
+      </c>
+      <c r="J8" s="15">
+        <v>32000</v>
+      </c>
+      <c r="K8" s="15">
+        <v>2</v>
+      </c>
+      <c r="L8" s="16">
+        <v>0</v>
+      </c>
+      <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
+      <c r="O8" s="14">
+        <v>0</v>
+      </c>
+      <c r="P8" s="13">
+        <v>2010</v>
+      </c>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="17">
+        <v>47.491300000000003</v>
+      </c>
+      <c r="S8" s="17">
+        <v>12.818199999999999</v>
+      </c>
+      <c r="T8" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="U8" s="18" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="10"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="14"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
+      <c r="O9" s="14"/>
+      <c r="P9" s="13"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="18"/>
+      <c r="U9" s="18"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" s="10"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="13"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="17"/>
+      <c r="S10" s="17"/>
+      <c r="T10" s="18"/>
+      <c r="U10" s="18"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="10"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
+      <c r="O11" s="14"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="18"/>
+      <c r="U11" s="18"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" s="10"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="17"/>
+      <c r="S12" s="17"/>
+      <c r="T12" s="18"/>
+      <c r="U12" s="18"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/data/fullyear-resilience/Power_VRES.xlsx
+++ b/data/fullyear-resilience/Power_VRES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\fullyear-resilience\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF8E5A6-7D41-4964-8C7A-665EB392C4C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0710EF86-E2C7-4168-A779-8864CEA15A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="41985" yWindow="2505" windowWidth="28800" windowHeight="15105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioA" sheetId="1" r:id="rId1"/>
@@ -1287,10 +1287,10 @@
         <v>1</v>
       </c>
       <c r="I8" s="13">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J8" s="15">
-        <v>200</v>
+        <v>32000</v>
       </c>
       <c r="K8" s="15">
         <v>2</v>

--- a/data/fullyear-resilience/Power_VRES.xlsx
+++ b/data/fullyear-resilience/Power_VRES.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simon Malacek\Code\LEGO-Pyomo\data\fullyear-resilience\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0710EF86-E2C7-4168-A779-8864CEA15A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D4D3B9B-B7DA-451C-B972-19A3853861D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41985" yWindow="2505" windowWidth="28800" windowHeight="15105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioA" sheetId="1" r:id="rId1"/>
@@ -1290,10 +1290,10 @@
         <v>20</v>
       </c>
       <c r="J8" s="15">
-        <v>32000</v>
+        <v>55000</v>
       </c>
       <c r="K8" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L8" s="16">
         <v>0</v>
